--- a/experimental_datasets/Semrau/Data/CardamomOT_inputs.xlsx
+++ b/experimental_datasets/Semrau/Data/CardamomOT_inputs.xlsx
@@ -207,6 +207,11 @@
         <t>Total population size at this timepoint</t>
       </text>
     </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional: dataset_id of the sample (empty or "all": default of the samples without rows)</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -440,6 +445,11 @@
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <t>Reference net proliferation rate (birth - death), in h^-1; without the inference stimulus if perturbation_inference gives its effect on this cell type (RATEk)</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional: dataset_id these anchors are for (empty or "all": default of the samples that have none of their own)</t>
       </text>
     </comment>
   </commentList>
@@ -987,11 +997,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1003,6 +1014,11 @@
       <c r="B1" s="4" t="inlineStr">
         <is>
           <t>net_rate_per_hour</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>sample_id</t>
         </is>
       </c>
     </row>
@@ -1018,11 +1034,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1034,6 +1051,11 @@
       <c r="B1" s="4" t="inlineStr">
         <is>
           <t>population_size</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>sample_id</t>
         </is>
       </c>
     </row>

--- a/experimental_datasets/Semrau/Data/CardamomOT_inputs.xlsx
+++ b/experimental_datasets/Semrau/Data/CardamomOT_inputs.xlsx
@@ -450,6 +450,16 @@
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <t>Optional: dataset_id these anchors are for (empty or "all": default of the samples that have none of their own)</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional reference birth (division) rate, in h^-1: anchors the birth rate of the cells of this type (dilution of the proteins); with the net rate, gives the death rate</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional reference death rate, in h^-1: anchors the death rate of the cells of this type; with the net rate, gives the birth rate</t>
       </text>
     </comment>
   </commentList>
@@ -822,7 +832,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Gene lists, one gene per row in each column. Any other column is a named gene list, usable as the targets (STIMk) or a RATE target of perturbation_inference and perturbation_simulation (exported as gene_list_&lt;name&gt;.txt; legacy Data/gene_list_&lt;name&gt;.txt).</t>
+          <t>Gene lists, one gene per row in each column. Any other column is a named gene list, usable as the targets (STIMk) or a RATE target of perturbation_inference and perturbation_simulation (exported as gene_list_&lt;name&gt;.txt).</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -869,7 +879,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Schedules of the simulations, one row per simulated timepoint: inference stimuli (stimulus_k, acting on the genes and, through the RATEk of perturbation_inference, on proliferation and death), then perturbation stimuli (STIMk, as in perturbation_simulation).</t>
+          <t>Schedules of the simulations: inference stimuli (stimulus_k, acting on the genes and, through the RATEk of perturbation_inference, on proliferation and death), then perturbation stimuli (STIMk, as in perturbation_simulation). Rows with a scenario name give alternative schedules (e.g. alternating inference and perturbation stimuli), simulated for the conditions that ask for them; a value applies to the simulated intervals ending at or after its time, so switching times should be simulated times.</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -937,7 +947,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Anchors of the net proliferation rates per cell type (get_proliferation_rates); every cell type needs a value.</t>
+          <t>Anchors of the proliferation rates per cell type (fit_population_anchors, get_proliferation_rates); every cell type needs a net rate, given directly or as birth - death. Birth and death, when given, anchor the two rates separately; otherwise the change of the net rate is shared between them. Rows with a sample_id anchor that sample only (a sample with rows of its own ignores the default ones); a sample without anchors borrows those of the best-fitting sample.</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -954,7 +964,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Absolute population sizes, anchoring the growth estimated by optimal transport.</t>
+          <t>Population sizes per sample and time: they constrain the absolute growth in fit_population_anchors and in the growth estimated by optimal transport.</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -971,7 +981,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Cell-type transition rate matrix constraining optimal transport: first column = source cell types, header = target cell types (as in obs cell_type_transition, else cell_type).</t>
+          <t>Cell-type transition rate matrix (Markov generator) constraining optimal transport through the probabilities expm(Q dt): first column = source cell types, header = target cell types (as in obs cell_type_transition, else cell_type). To give a matrix per sample, add a column sample_id right of the matrix (one value per row of the block, or one block per sample); rows without sample_id are the default of the samples without block of their own.</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -997,12 +1007,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1019,6 +1031,16 @@
       <c r="C1" s="4" t="inlineStr">
         <is>
           <t>sample_id</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>birth_rate_per_hour</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>death_rate_per_hour</t>
         </is>
       </c>
     </row>
